--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_05_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_05_18_Cau.xlsx
@@ -809,7 +809,7 @@
       <c r="J7" s="3" t="n"/>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không thể sửa để bám bằng chứng nếu chưa xác định mệnh đề nào thiếu hỗ trợ.</t>
+          <t>Quy trình tự sửa chữa bản nháp (self-correction workflow) bám sát bằng chứng: 1. Tách bản nháp thành các mệnh đề nguyên tử độc lập (o2) -&gt; 2. So sánh từng mệnh đề với context và gắn nhãn được hỗ trợ/mâu thuẫn/chưa có bằng chứng (o4) -&gt; 3. Áp dụng thao tác bỏ, sửa hoặc thử lại có giới hạn đối với mệnh đề chưa đạt (o3) -&gt; 4. Xuất câu trả lời cuối cùng hoặc thông báo từ chối trả lời (abstain) (o1).</t>
         </is>
       </c>
     </row>

--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_05_18_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_08_Full_112_Cau/Day_08_Ngan_Hang_Phan_05_18_Cau.xlsx
@@ -672,10 +672,22 @@
       <c r="K4" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Phân biệt trường hợp không có bằng chứng với trường hợp bằng chứng chưa đầy đủ.
-Phân tích theo nguyên lý thiết kế: Phân biệt trường hợp không có bằng chứng với trường hợp bằng chứng chưa đầy đủ.</t>
+- [Quyết định Abstain dứt khoát] (1.5 điểm): Chọn hành vi từ chối trả lời; cấm sử dụng kiến thức phổ biến từ trí nhớ LLM khi thiếu bằng chứng tenant/version.
+- [Biện minh bảo mật và cô lập Tenant] (1.0 điểm): Nêu rõ rủi ro sai lệch chính sách nội bộ và vi phạm cách ly dữ liệu giữa các tổ chức.
+- [Lời giải thích minh bạch cho người dùng] (1.5 điểm): Soạn thảo thông điệp giải thích rõ ràng cho người dùng và hướng dẫn kênh liên hệ chính thức.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn Hành vi Hệ thống (System Behavior Selection):
+Hệ thống bắt buộc phải thực hiện hành vi **TỪ CHỐI TRẢ LỜI CÓ NGUYÊN TẮC (Principled Abstention / Selective Abstention)**:
+- Mặc dù mô hình 'biết câu trả lời phổ biến' trong trọng số tham số (parametric memory), hệ thống **TUYỆT ĐỐI KHÔNG ĐƯỢC DÙNG KIẾN THỨC ĐÓ ĐỂ TRẢ LỜI**.
+- Lý do bảo mật &amp; tuân thủ: Tập đã truy xuất không có bản ghi nào thuộc đúng tenant và đúng phiên bản được phép. Việc sử dụng kiến thức chung ngoài luồng có thể dẫn đến hai rủi ro nghiêm trọng: (a) Rò rỉ kiến thức chéo tenant hoặc vi phạm chính sách riêng tư của doanh nghiệp; (b) Trả lời sai lệch so với quy định đặc thù của tổ chức mà người dùng thuộc về.
+2. Lời giải thích minh bạch và phù hợp cho người dùng (Transparent User Explanation):
+- Phản hồi chuẩn: 'Rất tiếc, hệ thống không tìm thấy tài liệu chính sách nào thuộc tổ chức của bạn và đang có hiệu lực thi hành liên quan đến câu hỏi này. Để đảm bảo tính chính xác và tuân thủ quy định nội bộ, hệ thống không thể cung cấp câu trả lời suy đoán. Vui lòng liên hệ bộ phận hỗ trợ của tổ chức bạn để được giải đáp.'
+3. Phân biệt kỹ thuật:
+Đây là trường hợp **Không có bằng chứng hợp lệ (Zero Eligible Evidence)** trong phạm vi thẩm quyền của người dùng, khác hoàn toàn với trường hợp có bằng chứng nhưng chưa đầy đủ.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Bức tường Tenant (Tenant Isolation) và Phòng thủ Ảo giác: Một hệ thống RAG doanh nghiệp phải coi Cơ sở tri thức Tenant là nguồn sự thật duy nhất (Ground Truth). Khi không có tài liệu hợp lệ trong không gian thẩm quyền, việc từ chối trả lời (Abstain) là hành vi thể hiện tính tin cậy và an toàn cao nhất của AI.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE / AI Safety: 'Selective Abstention in Enterprise RAG' &amp; Microsoft Multi-tenant Security Patterns</t>
         </is>
       </c>
     </row>
@@ -754,10 +766,25 @@
       <c r="K6" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt quy tắc chỉ dùng bằng chứng và quy tắc citation.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt quy tắc chỉ dùng bằng chứng và quy tắc citation.</t>
+- [Sửa vị trí đặt quy tắc dạng Sandwich] (1.5 điểm): Chuyển quy tắc lên System prompt và nhắc lại ở cuối prompt ngay sát câu hỏi (Sandwich Prompting).
+- [Thiết kế bước hậu kiểm Entailment] (1.0 điểm): Định nghĩa bước kiểm tra đối chiếu câu trả lời với context sau khi sinh.
+- [Hành động xử lý &amp; Điều kiện dừng hữu hạn] (1.5 điểm): Thiết lập cơ chế thử lại tối đa 1 lần, nếu vẫn sai thì fallback cứng về chuỗi từ chối, bảo đảm kết thúc hữu hạn.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Sửa đổi vị trí đặt quy tắc (Prompt Structure Optimization):
+- Phân tích nguyên nhân: Đặt quy tắc 'nếu thiếu evidence thì phải abstain' ở sau một đoạn context quá dài sẽ khiến quy tắc bị trôi dạt ra xa khỏi sự chú ý của mô hình (Recency/Primacy Bias Defect), dẫn đến việc mô hình bỏ qua quy tắc.
+- **Vị trí sửa đổi chuẩn mực**:
+  + **Đặt ở Đầu Prompt (System Instructions Block)**: Khẳng định rõ ràng như một chỉ thị tối thượng (Primary Directive).
+  + **Đồng thời nhắc lại ở Cuối Prompt (Final Immediate Suffix / Sandwich Defense)**: Ngay sau đoạn context và ngay trước thẻ câu hỏi: `[LƯU Ý CUỐI: Chỉ trả lời nếu có bằng chứng trực tiếp trong các đoạn trên; nếu thiếu, bắt buộc trả lời 'Không có đủ thông tin'].`
+2. Thiết kế Bước Hậu kiểm Bằng chứng (Post-generation Evidence Guardrail):
+- **Hành động xử lý (Deterministic Verification)**: Chạy một bộ kiểm tra NLI / Entailment nhẹ hoặc Regex Citation Checker để đối chiếu từng câu trả lời với context:
+  + Nếu câu trả lời không trích dẫn nguồn hợp lệ hoặc chứa các khẳng định không có trong context, hệ thống kích hoạt cơ chế can thiệp (Intervention).
+- **Điều kiện dừng hữu hạn (Finite Stopping Condition)**:
+  + Hệ thống gửi lại prompt kèm phản hồi sửa lỗi (Feedback Correction) cho LLM tối đa **1 lần thử lại (Max Retries = 1)**.
+  + Nếu sau 1 lần thử lại mà câu trả lời vẫn không tuân thủ nguyên tắc bám bằng chứng, hệ thống lập tức can thiệp bằng code cứng (Hard Fallback): Thay thế toàn bộ đầu ra bằng chuỗi từ chối chuẩn: 'Hệ thống từ chối trả lời do không đủ bằng chứng tin cậy trong tài liệu tham khảo.' (Dừng hữu hạn, không lặp vô tận).
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Kỹ thuật 'Sandwich Defense' (đặt chỉ dẫn ở cả đầu và cuối prompt) giúp củng cố sự chú ý của mô hình ngôn ngữ lớn đối với các quy tắc an toàn. Kết hợp với bộ hậu kiểm có số vòng thử lại hữu hạn (Finite Retries) và phương án dự phòng cứng (Deterministic Fallback) bảo đảm hệ thống luôn hội tụ và không bao giờ bị rơi vào vòng lặp vô tận.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Anthropic Prompt Engineering: 'The Sandwich Technique for Long Prompts' &amp; OWASP LLM01 Mitigations</t>
         </is>
       </c>
     </row>
@@ -840,10 +867,26 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt việc tách mệnh đề và đối chiếu với context.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt việc tách mệnh đề và đối chiếu với context.</t>
+- [Phê phán cách kiểm tra tự xác nhận] (1.5 điểm): Chỉ ra lỗi không cấp context khiến verifier mắc bẫy tự xác nhận (sycophancy) và ảo giác lặp lại.
+- [Quy trình tách mệnh đề &amp; đối chiếu NLI] (1.5 điểm): Mô tả rõ quy trình: tách claim nguyên tử và đối chiếu logic với context thực tế.
+- [Hành động sửa &amp; Điều kiện dừng hữu hạn] (1.0 điểm): Thiết lập cơ chế sửa với giới hạn tối đa 1 loop, cắt bỏ câu lỗi nếu không sửa được để bảo đảm dừng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá cách kiểm tra hiện tại (Critique of Current Verifier):
+Cách kiểm tra này là **HOÀN TOÀN VÔ GIÁ TRỊ VÀ MANG TÍNH TỰ THỎA MÃN (Self-Affirmation Flaw)**:
+- Việc hỏi mô hình 'câu trả lời có đúng không?' mà không cung cấp tài liệu ngữ cảnh (Context) là một sai lầm chết người. Mô hình chỉ kiểm tra lại bộ nhớ tham số vốn dĩ đã sinh ra lỗi đó; các nghiên cứu đã chứng minh LLM luôn có xu hướng thiên vị tự xác nhận (Self-Consistency Bias / Sycophancy), luôn trả lời 'đúng' ngay cả khi vừa bịa đặt hoàn toàn.
+2. Quy trình kiểm tra bằng chứng cụ thể thay thế (Evidence-Grounded Verification Loop):
+- **Bước 1: Phân tách Mệnh đề Nguyên tử (Atomic Claim Extraction)**:
+  Chạy một prompt hoặc thuật toán tách câu trả lời thành danh sách các mệnh đề độc lập: `[Claim_1, Claim_2, ...]`. Ví dụ: 'Học phí là 10 triệu' (Claim 1), 'Hạn nộp là 30/9' (Claim 2).
+- **Bước 2: Đối chiếu Mệnh đề với Ngữ cảnh (Claim-to-Context Entailment Check)**:
+  Cung cấp Context thực tế cho Verifier và yêu cầu đánh giá từng mệnh đề theo 3 nhãn NLI: `Supported` (Được hỗ trợ), `Contradicted` (Mâu thuẫn), hoặc `Unverifiable` (Không có bằng chứng).
+- **Bước 3: Hành động xử lý và Điều kiện dừng hữu hạn (Correction &amp; Finite Stop)**:
+  + Nếu tất cả mệnh đề đều là `Supported`: Phê duyệt câu trả lời và trả về người dùng.
+  + Nếu có mệnh đề `Unverifiable` hoặc `Contradicted`: Gửi phản hồi cụ thể cho Generator yêu cầu viết lại, chỉ giữ lại các mệnh đề `Supported`.
+  + **Điều kiện dừng hữu hạn**: Giới hạn tối đa **1 lần sửa (Max Loops = 1)**. Nếu sau 1 lần sửa vẫn còn mệnh đề không có bằng chứng, hệ thống tự động loại bỏ các câu vi phạm bằng code cắt lọc hoặc trả về thông báo từ chối.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc Self-Correction đáng tin cậy: Mô hình không thể tự sửa lỗi nếu không có dữ liệu đối chứng bên ngoài (Grounded Reference Context). Quy trình tách mệnh đề nguyên tử và đối chiếu logic (Claim Decomposition and Entailment Checking) là phương pháp khoa học duy nhất giúp phát hiện và loại bỏ ảo giác.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Asai et al. (2023): 'Self-RAG: Learning to Retrieve, Generate, and Critique through Self-Reflection' &amp; TruLens Groundedness Engine</t>
         </is>
       </c>
     </row>
@@ -874,10 +917,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt tập evidence bắt buộc và context đã truy xuất.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt tập evidence bắt buộc và context đã truy xuất.</t>
+- [Tính toán chính xác Context Recall = 2/3] (2.0 điểm): Xác định đúng công thức, tính ra 2/3 = 0.67 (66.7%) và đánh giá chưa đạt yêu cầu.
+- [Chỉ rõ dữ kiện còn thiếu] (1.0 điểm): Nêu chính xác dữ kiện bị thiếu là 'Người phê duyệt'.
+- [Phân tích hậu quả đối với bước Generation] (1.0 điểm): Phân tích rõ việc thiếu dữ kiện dẫn đến câu trả lời bị cụt hoặc kích hoạt ảo giác bịa chức danh.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Chỉ số Context Recall (Context Recall Assessment):
+- Công thức Context Recall: `Context Recall = (Số dữ kiện bắt buộc có trong Context đã truy xuất) / (Tổng số dữ kiện bắt buộc cần thiết)`.
+- Phân tích dữ kiện:
+  + Tập dữ kiện bắt buộc: `{Điều kiện, Hạn chót, Người phê duyệt}` (Tổng số = 3 dữ kiện).
+  + Tập dữ kiện có trong các chunk đã truy xuất: `{Điều kiện, Hạn chót}` (Số lượng bao phủ = 2 dữ kiện).
+- **Tính toán điểm số**: `Context Recall = 2 / 3 = 0.67` (hoặc xấp xỉ 66.7%).
+- Đánh giá: Context Recall đạt mức **TRUNG BÌNH THẤP / KHÔNG ĐẠT YÊU CẦU HOÀN THIỆN**.
+2. Chỉ ra Bằng chứng còn thiếu và Hậu quả (Missing Evidence &amp; Impact):
+- Bằng chứng còn thiếu: **Dữ kiện về 'Người phê duyệt' (Approver Fact)**.
+- Hậu quả đối với mô hình tạo sinh: Do ngữ cảnh thiếu hoàn toàn thông tin về người phê duyệt, nếu mô hình được yêu cầu trả lời đầy đủ, nó sẽ buộc phải đối mặt với hai kịch bản xấu: hoặc là từ chối trả lời một phần câu hỏi, hoặc là tạo sinh ảo giác (hallucination) tự bịa ra một chức danh người phê duyệt không có thật trong chính sách.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Context Recall đo lường mức độ đầy đủ của ngữ cảnh truy xuất so với câu trả lời chuẩn (Ground-Truth Answer). Nếu Context Recall &lt; 1.0, tầng tạo sinh sẽ bị thiếu thông tin đầu vào. Để sửa lỗi này, cần tối ưu hóa tầng retrieval (tăng K, mở rộng query, hoặc kiểm tra lại kích thước phân đoạn tài liệu).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Es et al. (2023): 'Ragas: Automated Evaluation of Retrieval Augmented Generation' - Context Recall Definition</t>
         </is>
       </c>
     </row>
@@ -908,10 +965,23 @@
       <c r="K10" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Đối chiếu tập evidence bắt buộc với context đã truy xuất.
-Phân tích theo nguyên lý thiết kế: Đối chiếu tập evidence bắt buộc với context đã truy xuất.</t>
+- [Đánh giá Context Recall đạt tối đa 1.0] (1.5 điểm): Xác định Context Recall rất cao (100%) vì có đủ cả 4 dữ kiện bắt buộc.
+- [Xác định đúng Metric phản ánh nhiễu] (1.5 điểm): Chỉ ra Context Precision (hoặc Context Relevance / Noise Ratio) là metric phản ánh 2 chunk không liên quan.
+- [Đề xuất giải pháp xử lý nhiễu] (1.0 điểm): Đề xuất sử dụng Reranker hoặc similarity threshold để lọc bỏ chunk rác, nâng cao Precision.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Chỉ số Context Recall (Context Recall Assessment):
+- Phân tích: Câu trả lời tham chiếu cần 4 dữ kiện cốt lõi; tập ngữ cảnh đã truy xuất bao phủ trọn vẹn cả 4 dữ kiện này (`4 / 4 = 1.0`).
+- Kết luận: **Context Recall ĐẠT MỨC TUYỆT ĐỐI (Context Recall = 1.0 / 100%)**.
+2. Metric phản ánh phần nhiễu trong tập đã truy xuất (Noise Reflection Metric):
+- Chỉ số phản ánh chính xác lượng nhiễu (2 chunk không liên quan) là **Context Precision** (hoặc **Context Relevance / Noise Ratio**):
+  + **Context Precision (Độ chuẩn xác ngữ cảnh)**: Đo lường tỷ lệ các chunk thực sự liên quan và hữu ích trên tổng số chunk được truy xuất vào context, đồng thời tính đến thứ hạng xếp hạng của các chunk liên quan. Với 2 chunk không liên quan chen vào, Context Precision bị sụt giảm đáng kể.
+  + **Noise Ratio (Tỷ lệ nhiễu)**: `Noise Ratio = 2 / (Tổng số chunks truy xuất)`. Thể hiện lượng token lãng phí và nguy cơ làm loãng sự chú ý của LLM.
+3. Ý nghĩa kiến trúc:
+Hệ thống đã giải quyết xong bài toán Recall (không bị sót bằng chứng), nhưng đang gặp vấn đề về Precision. Giải pháp cần áp dụng là bổ sung Cross-Encoder Reranker để lọc bỏ 2 chunk nhiễu trước khi nạp vào LLM.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Context Recall cao không đồng nghĩa với chất lượng truy xuất hoàn hảo nếu đi kèm với Context Precision thấp. Lượng chunk nhiễu lọt vào context sẽ làm tăng chi phí tính toán, tăng độ trễ suy luận và có thể dẫn đến hiện tượng mô hình bị phân tán sự chú ý (Distraction / Context Poisoning).
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+TruLens Documentation: 'Context Relevance Metric' &amp; Ragas 'Context Precision and Context Recall'</t>
         </is>
       </c>
     </row>
@@ -990,10 +1060,21 @@
       <c r="K12" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra lần lượt quan hệ hỗ trợ giữa mệnh đề và bằng chứng, rồi các mệnh đề chưa được hỗ trợ.
-Phân tích theo nguyên lý thiết kế: Kiểm tra lần lượt quan hệ hỗ trợ giữa mệnh đề và bằng chứng, rồi các mệnh đề chưa được hỗ trợ.</t>
+- [Đánh giá Faithfulness thấp do có số bịa] (1.5 điểm): Khẳng định độ bám bằng chứng không đạt vì chứa con số không xuất hiện trong context.
+- [Định nghĩa và phân biệt rõ Answer Relevance] (1.5 điểm): Giải thích rõ Relevance đo việc trả lời đúng ý định (ở đây đạt cao), còn Faithfulness đo tính trung thực với context (ở đây bị rớt).
+- [Tổng kết nguyên lý RAG Triad] (1.0 điểm): Nhấn mạnh một câu trả lời có thể vừa high-relevance vừa low-faithfulness.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Độ bám bằng chứng (Faithfulness / Groundedness Assessment):
+- Đánh giá: **Độ bám bằng chứng KÉM / KHÔNG ĐẠT (Low Faithfulness / Hallucination Detected)**.
+- Căn cứ kỹ thuật: Câu trả lời đã tự ý bổ sung một con số định lượng hoàn toàn không xuất hiện trong ngữ cảnh (Context). Trong đánh giá RAG, một câu trả lời chỉ được coi là Faithful khi 100% các mệnh đề và thực thể số liệu đều được suy diễn trực tiếp từ bằng chứng. Việc đưa ra con số vô căn cứ là biểu hiện điển hình của lỗi ảo giác tự sinh (Extrinsic Hallucination).
+2. Phân biệt rạch ròi giữa Độ bám bằng chứng (Faithfulness) và Độ liên quan (Answer Relevance):
+- **Answer Relevance (Độ liên quan của câu trả lời)**: Đo lường xem câu trả lời có **đi thẳng vào trọng tâm câu hỏi của người dùng hay không** (Addresses the user's intent). Đề bài nêu rõ câu trả lời 'rất đúng trọng tâm người dùng', do đó Answer Relevance đạt điểm rất cao (gần 1.0).
+- **Faithfulness (Độ bám bằng chứng)**: Đo lường xem câu trả lời có **trung thực và được chứng minh bởi tài liệu tham khảo hay không** (Grounded in context). Ở đây, do có con số bịa đặt, Faithfulness bị đánh rớt xuống mức thấp.
+3. Kết luận: Một câu trả lời có thể cực kỳ liên quan (Relevance cao) nhưng lại hoàn toàn sai sự thật / ảo giác (Faithfulness thấp). Đây là lý do vì sao bộ đánh giá RAG Triad bắt buộc phải tách riêng hai chỉ số này.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự tách biệt giữa Faithfulness và Answer Relevance là nền tảng của khung đánh giá RAG Triad (TruLens / Ragas). Một mô hình nịnh người dùng (Sycophantic / Over-helpful LLM) thường tạo ra câu trả lời rất trôi chảy, đúng ý người hỏi nhưng lại tự bịa thêm số liệu chi tiết để nghe có vẻ thuyết phục. Nhận diện sự mâu thuẫn này là năng lực cốt lõi của kỹ sư kiểm thử AI.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+TruLens: 'The RAG Triad - Groundedness, Answer Relevance, Context Relevance' (https://www.trulens.org)</t>
         </is>
       </c>
     </row>
@@ -1072,10 +1153,23 @@
       <c r="K14" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định ý định của câu hỏi, rồi kiểm tra câu trả lời có đi thẳng vào ý định đó hay không.
-Phân tích theo nguyên lý thiết kế: Xác định ý định của câu hỏi, rồi kiểm tra câu trả lời có đi thẳng vào ý định đó hay không.</t>
+- [Chỉ rõ lỗi né tránh ý định so sánh A và B] (1.5 điểm): Phân tích người dùng hỏi so sánh/chọn giữa A và B nhưng câu trả lời chỉ nói về A, né tránh B và không có khuyến nghị.
+- [Đánh giá sụt giảm Answer Relevance] (1.0 điểm): Khẳng định điểm Relevance bị phạt thấp do không giải quyết đúng ý định cốt lõi.
+- [Cấu trúc câu trả lời chuẩn hóa] (1.5 điểm): Đưa ra khung trả lời đúng trọng tâm: so sánh 2 bên, phân tích đánh đổi và kết luận khuyến nghị.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chỉ ra lỗi nghiêm trọng về Answer Relevance (Defect Localization):
+- Câu hỏi của người dùng có ý định so sánh và đưa ra quyết định lựa chọn: **'Nên chọn A hay B?'** (Trade-off &amp; Decision Query).
+- Phân tích lỗi của câu trả lời:
+  + **Lạc hướng Ý định (Intent Mismatch / Evasion Defect)**: Câu trả lời giải thích A rất dài nhưng hoàn toàn bỏ qua thực thể B, không đưa ra bất kỳ bảng so sánh tiêu chí nào giữa A và B, và không đưa ra khuyến nghị lựa chọn có căn cứ.
+  + **Điểm Answer Relevance Thấp**: Mặc dù văn bản giải thích A rất mạch lạc, nhưng vì không trả lời đúng câu hỏi 'nên chọn cái nào giữa A và B', điểm Answer Relevance bị phạt nặng (thường &lt; 0.40).
+2. Đề xuất cấu trúc câu trả lời chuẩn mực đạt Answer Relevance cao:
+- **Phần 1: Trả lời trực diện khuyến nghị**: 'Để lựa chọn giữa A và B, khuyến nghị phụ thuộc vào ưu tiên của bạn: chọn A nếu cần... và chọn B nếu ưu tiên...'
+- **Phần 2: Bảng so sánh đối chiếu đa tiêu chí giữa A và B** (Hiệu năng, Chi phí, Độ phức tạp triển khai).
+- **Phần 3: Kết luận tóm tắt** giúp người dùng đưa ra quyết định dứt khoát.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Answer Relevance đánh giá mức độ câu trả lời giải quyết trực tiếp câu hỏi được hỏi. Việc nói dài dòng về một chủ đề phụ nhưng né tránh câu hỏi chính là lỗi điển hình của các hệ thống thiếu bộ định hướng câu trả lời (Intent Alignment). Đạt Relevance cao đòi hỏi phải trả lời trực diện vào tất cả các vế của câu hỏi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Es et al. (2023): 'Ragas: Automated Evaluation of Retrieval Augmented Generation' - Answer Relevance Calculation</t>
         </is>
       </c>
     </row>
@@ -1154,10 +1248,23 @@
       <c r="K16" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giữ corpus, tập kiểm thử và baseline cố định trước khi so sánh.
-Phân tích theo nguyên lý thiết kế: Giữ corpus, tập kiểm thử và baseline cố định trước khi so sánh.</t>
+- [Đề xuất triển khai chọn lọc theo nhóm query] (1.5 điểm): Đề xuất bật Reranker cho query khó và tắt (bypass) cho query ngắn để tối ưu cả hai phía.
+- [Biện minh bác bỏ 2 thái cực] (1.5 điểm): Giải thích rõ không bật toàn diện vì làm giảm chất lượng query ngắn, không hoàn tác vì mất lợi ích query khó.
+- [Yêu cầu công bố Product SLA &amp; Threshold] (1.0 điểm): Nhấn mạnh sự cần thiết của việc xác định ưu tiên sản phẩm để làm chuẩn nghiệm thu chính thức.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đề xuất có điều kiện dựa trên bằng chứng thực nghiệm hiện có (Conditional Proposal):
+- Quyết định: **ÁP DỤNG RERANKER CÓ ĐIỀU KIỆN THEO ĐỊNH TUYẾN PHÂN NHÓM QUERY (Route-based Selective Deployment)**, TUYỆT ĐỐI KHÔNG triển khai toàn diện và KHÔNG hoàn tác toàn bộ:
+  + **Nhóm 1 (Query khó / Phức tạp / Đa chặng)**: Bật Reranker. Bằng chứng thực nghiệm xác nhận Reranker giúp tăng đáng kể Recall ở nhóm query này, mang lại giá trị cao cho người dùng.
+  + **Nhóm 2 (Query ngắn / FAQ / Tìm kiếm từ khóa đơn giản)**: Tắt Reranker (Bypass Reranking, dùng trực tiếp kết quả First-stage). Bằng chứng cho thấy Reranker làm giảm độ liên quan ở query ngắn, việc bypass vừa giữ chất lượng cao vừa tiết kiệm độ trễ.
+2. Lý do không triển khai toàn diện và không hoàn tác:
+- Không triển khai toàn bộ vì điểm trung bình tổng chỉ tăng nhẹ nhưng lại làm suy thoái chất lượng câu trả lời ở nhóm query ngắn và tốn thêm chi phí độ trễ p95.
+- Không hoàn tác toàn bộ vì việc hoàn tác sẽ vứt bỏ hoàn toàn mức tăng Recall có giá trị trên nhóm query khó.
+3. Điều kiện tiên quyết cần thiết lập tiếp theo:
+- Phối hợp với Product Owner công bố rõ ràng Bảng Ưu tiên Trọng số Sản phẩm (Product Trade-off SLA): Xác định rõ sản phẩm ưu tiên độ chính xác tuyệt đối trên query khó hay ưu tiên độ trễ và sự ngắn gọn trên query ngắn để thiết lập threshold chính thức.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong tinh chỉnh RAG có kiểm soát (Controlled RAG Tuning), giải pháp 'All-or-Nothing' (bật cho tất cả hoặc tắt tất cả) là tư duy thô sơ. Một kỹ sư chuyên nghiệp sẽ sử dụng dữ liệu thực nghiệm để xây dựng bộ định tuyến chọn lọc (Selective Router): áp dụng giải pháp đắt đỏ ở nơi nó tạo ra giá trị vượt trội và bỏ qua ở nơi nó gây tác dụng phụ.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Principles: 'Controlled Canary Rollouts &amp; Subgroup Feature Gating'</t>
         </is>
       </c>
     </row>
@@ -1236,10 +1343,25 @@
       <c r="K18" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Kiểm tra tập evaluation có phiên bản và lệnh chạy có thể tái lập.
-Phân tích theo nguyên lý thiết kế: Kiểm tra tập evaluation có phiên bản và lệnh chạy có thể tái lập.</t>
+- [Nhận diện lỗi gãy liên kết trích dẫn] (1.0 điểm): Chỉ ra formatter đổi ID làm hỏng 8% citation dù retrieval metric không đổi.
+- [Thiết kế Hard Gate với Zero Tolerance] (1.5 điểm): Thiết lập cổng chặn CI/CD với tiêu chí nghiêm ngặt Broken Citation Rate == 0%.
+- [Quy trình kiểm thử tự động hóa có thể tái lập] (1.5 điểm): Mô tả lệnh kiểm thử tự động hóa giải mã citation ID trên tập evaluation cố định trước khi release.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Phân tích nguyên nhân sự cố:
+Mặc dù các chỉ số truy xuất truyền thống (Recall, MRR) không đổi, nhưng việc Code Formatter tự ý thay đổi cú pháp hoặc quy ước ID citation đã khiến 8% liên kết trích dẫn bị gãy (Broken Citations / 404 Links), làm phá hủy hoàn toàn khả năng tự xác minh nguồn của người dùng.
+2. Thiết kế Cổng Phát hành Kiểm thử Tự động (Release Gate Architecture):
+Thiết lập một Cổng kiểm soát bắt buộc trong pipeline CI/CD (Deployment Quality Gate) mà mọi bản build phải vượt qua 100% trước khi triển khai lên Production:
+- **Cổng 1 (Citation Link Integrity Check - Hard Gate / Zero Tolerance)**:
+  + Chạy kiểm thử tự động trên tập testset đánh giá đã đóng băng (Frozen Golden Testset).
+  + Thực hiện giải mã và 'click ảo' (Headless Verification) vào 100% các citation ID sinh ra trong câu trả lời.
+  + **Quy tắc chặn nghiêm ngặt (Hard Blocker)**: `Broken Citation Rate == 0.0%`. Bất kỳ bản build nào có tỷ lệ citation hỏng &gt; 0% đều bị lập tức hủy lệnh release (Rollback / Abort Deployment).
+- **Cổng 2 (E2E Regression Gate)**:
+  + Kiểm tra tính toàn vẹn của mã nguồn: Mã formatter không được phép can thiệp vào các trường ID khóa chính của metadata tài liệu.
+  + Lệnh kiểm thử có thể tái lập hoàn toàn (Deterministic &amp; Reproducible CI Command): `pytest tests/test_citation_integrity.py --strict`.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Một hệ thống RAG không chỉ được đánh giá bằng điểm số mô hình (Retrieval &amp; Generation metrics) mà còn phải được bảo vệ bởi các tiêu chuẩn kỹ thuật phần mềm (Software Reliability Engineering). Một thay đổi nhỏ ở tầng format code làm gãy 8% liên kết là một lỗi nghiêm trọng (Severe Regression) phải bị chặn đứng tự động tại CI/CD Release Gate.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE / Continuous Delivery: 'Deployment Gates and Automated Canary Analysis' &amp; ISO 25010 Software Quality</t>
         </is>
       </c>
     </row>
@@ -1270,10 +1392,25 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định chunk nào liên quan, rồi kiểm tra vị trí xếp hạng của chúng.
-Phân tích theo nguyên lý thiết kế: Xác định chunk nào liên quan, rồi kiểm tra vị trí xếp hạng của chúng.</t>
+- [Đánh giá chính xác Precision@5 = 40% và Nhiễu 60%] (1.5 điểm): Tính toán đúng và phân tích việc 3/5 chunk là nhiễu, đặc biệt chunk 2 làm gián đoạn rank.
+- [Cấm nhầm lẫn với lỗi thiếu bằng chứng] (1.0 điểm): Khẳng định rõ đây không phải lỗi thiếu bằng chứng (Recall) vì các chunk đúng vẫn hiện diện.
+- [Đề xuất xử lý đúng tầng Reranking] (1.5 điểm): Đưa ra giải pháp chuẩn: Cross-Encoder reranker và similarity cutoff threshold để thanh lọc nhiễu.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Đánh giá Context Precision và Mức độ Nhiễu:
+- Dữ liệu quan sát: Nhãn liên quan của 5 chunk đã xếp hạng là `[1, 0, 1, 0, 0]`.
+- Đánh giá Precision: Trong Top-5 chỉ có 2 chunk liên quan (ở vị trí 1 và 3). `Precision@5 = 2 / 5 = 0.40` (40%).
+- Đánh giá Mức độ Nhiễu (Noise Level): Có tới 3 chunk hoàn toàn không liên quan (ở các vị trí 2, 4, 5). Mức độ nhiễu chiếm **60% toàn bộ vùng ngữ cảnh**!
+- Đánh giá thứ hạng: Vị trí thứ 2 bị chiếm dụng bởi một chunk không liên quan, làm gián đoạn dòng chảy thông tin giữa chunk 1 và chunk 3.
+2. Phân định ranh giới lỗi và Đề xuất xử lý ở ĐÚNG TẦNG KIẾN TRÚC:
+- **Cảnh báo quan trọng**: Tuyệt đối **KHÔNG ĐƯỢC NHẦM** đây là lỗi thiếu bằng chứng (Recall Defect). Bằng chứng liên quan vẫn có mặt trong danh sách (ở rank 1 và 3).
+- Lỗi này thuộc về **TẦNG TÁI XẾP HẠNG VÀ TINH LỌC ỨNG VIÊN (Reranking &amp; Filtering Layer)**.
+- **Giải pháp xử lý đúng tầng**:
+  + Áp dụng mô hình **Cross-Encoder Reranker** mạnh hơn ở giai đoạn 2 để đẩy chunk liên quan ở vị trí 3 lên vị trí 2, và dìm các chunk không liên quan xuống cuối.
+  + Áp dụng **Ngưỡng điểm tương đồng tối thiểu (Similarity Score Cutoff)** để cắt tỉa các chunk rác ở vị trí 4 và 5 trước khi đưa vào prompt của LLM.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Context Precision thấp là biểu hiện của việc phễu truy xuất bị rò rỉ nhiễu (Noisy Context Window). Không được cố gắng sửa lỗi này bằng cách tăng thêm K ở retriever (vì sẽ càng làm tăng nhiễu), mà phải giải quyết ở tầng Reranking và Thresholding.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Es et al. (2023): 'Ragas: Automated Evaluation of Retrieval Augmented Generation' - Context Precision Metric</t>
         </is>
       </c>
     </row>
@@ -1304,10 +1441,24 @@
       <c r="K20" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Xác định các chunk liên quan và vị trí xếp hạng của chúng.
-Phân tích theo nguyên lý thiết kế: Xác định các chunk liên quan và vị trí xếp hạng của chúng.</t>
+- [Xác định đúng Metric Context Precision bị hỏng] (1.5 điểm): Chỉ ra Context Precision sụp đổ (chỉ đạt 20%) và tỷ lệ nhiễu lên tới 80% (12/15 chunk rác).
+- [Phân tích nguy cơ tràn context] (1.0 điểm): Nêu rõ nguy cơ lãng phí token, tăng độ trễ và xao nhãng LLM.
+- [Đề xuất 2 giải pháp kỹ thuật cụ thể] (1.5 điểm): Giảm K từ 15 xuống 4-5 và tích hợp Cross-Encoder Reranker lọc rác bằng score threshold.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Xác định Metric gặp vấn đề nghiêm trọng:
+- Metric có vấn đề nghiêm trọng nhất là **Context Precision (Độ chuẩn xác ngữ cảnh)** và **Signal-to-Noise Ratio (Tỷ lệ tín hiệu trên nhiễu)**:
+  + Chỉ có 3 trong 15 chunk là liên quan (chứa đủ dữ kiện), trong khi có tới **12 trong 15 chunk là hoàn toàn không liên quan (Tỷ lệ nhiễu lên tới 80%)**.
+  + Mặc dù Context Recall đạt 100% (chứa đủ dữ kiện), nhưng Context Precision sụp đổ xuống mức thảm hại: `3 / 15 = 0.20` (20%).
+- Hậu quả: Tràn ngập 12 chunk rác làm tràn context window của LLM, lãng phí token ngân sách, tăng độ trễ suy luận và tăng nguy cơ gây ảo giác hoặc bỏ quên thông tin cốt lõi (Lost in the Middle).
+2. Cách khắc phục phù hợp ở đúng tầng kiến trúc:
+- **Khắc phục 1: Giảm mạnh Top-K hoặc Thắt chặt Candidate Depth**:
+  Thu hẹp số lượng chunk gửi vào LLM từ `k = 15` xuống `k = 4` hoặc `k = 5`.
+- **Khắc phục 2: Triển khai Cross-Encoder Reranker kết hợp Score Thresholding**:
+  Chạy Cross-Encoder trên 15 candidate ban đầu để xếp hạng lại độ liên quan thực tế. Chỉ chọn lọc Top-3 đến Top-5 chunk có điểm số vượt ngưỡng sàn (`score &gt;= threshold`), loại bỏ hoàn toàn 12 chunk không liên quan trước khi đóng gói context prompt.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Việc nhồi nhét quá nhiều chunk (k=15) vào context chỉ để 'bắt cho hết bằng chứng' là một sai lầm phổ biến. Context bị ô nhiễm bởi 80% rác sẽ làm suy giảm nghiêm trọng khả năng lập luận của LLM. Tinh gọn context bằng Reranker và giảm K là biện pháp chuẩn tắc.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Cohere Rerank Best Practices &amp; TruLens Context Relevance Optimization Guides</t>
         </is>
       </c>
     </row>
